--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>93133328</v>
+        <v>136650812</v>
       </c>
       <c r="B15" t="n">
-        <v>101326</v>
+        <v>9417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,49 +2198,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>101246</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Spetsamåla, Bl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532402</v>
+        <v>532411</v>
       </c>
       <c r="R15" t="n">
-        <v>6256638</v>
+        <v>6256809</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,12 +2256,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,23 +2285,137 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jenny Ström Åkesson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jenny Ström Åkesson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136650812</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>93133328</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Spetsamåla, Bl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>532402</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6256638</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sillhövda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-05-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-05-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenny Ström Åkesson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenny Ström Åkesson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/93133328</t>
         </is>
@@ -2316,6 +2437,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>136428382</v>
       </c>
       <c r="B5" t="n">
-        <v>92511</v>
+        <v>92514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>136428382</v>
       </c>
       <c r="B5" t="n">
-        <v>92514</v>
+        <v>92515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>136428382</v>
       </c>
       <c r="B5" t="n">
-        <v>92515</v>
+        <v>92520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>136428382</v>
       </c>
       <c r="B5" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>136428382</v>
       </c>
       <c r="B5" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>136428382</v>
       </c>
       <c r="B5" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>136428382</v>
       </c>
       <c r="B5" t="n">
-        <v>92526</v>
+        <v>92527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -2190,7 +2190,7 @@
         <v>136650812</v>
       </c>
       <c r="B15" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 2527-2024 artfynd.xlsx
+++ b/artfynd/S 2527-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,10 +2308,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>93133328</v>
+        <v>137384212</v>
       </c>
       <c r="B16" t="n">
-        <v>101326</v>
+        <v>9424</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2319,49 +2319,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>101246</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Spetsamåla, Bl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532402</v>
+        <v>532472</v>
       </c>
       <c r="R16" t="n">
-        <v>6256638</v>
+        <v>6256481</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2385,12 +2377,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Död hane</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,23 +2406,137 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jenny Ström Åkesson</t>
+          <t>Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jenny Ström Åkesson</t>
+          <t>Via Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137384212</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>93133328</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Spetsamåla, Bl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>532402</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6256638</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sillhövda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-05-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-05-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenny Ström Åkesson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jenny Ström Åkesson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/93133328</t>
         </is>
@@ -2438,6 +2559,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
